--- a/demo_data/sectors/perakende_eticaret/mizan_prior.xlsx
+++ b/demo_data/sectors/perakende_eticaret/mizan_prior.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,16 +523,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>108.01</t>
+          <t>120.01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kredi Kartı &amp; POS Tahsilatları</t>
+          <t>Cari Müşteri 01 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1049866.52</v>
+        <v>163019.49</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -541,16 +541,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>120.01</t>
+          <t>120.02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cari Müşteri 01 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 02 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48905.85</v>
+        <v>152503.64</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -559,16 +559,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>120.02</t>
+          <t>120.03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cari Müşteri 02 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 03 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45751.09</v>
+        <v>142152.59</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -577,16 +577,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>120.03</t>
+          <t>120.04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cari Müşteri 03 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 04 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42645.78</v>
+        <v>131972.71</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -595,16 +595,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>120.04</t>
+          <t>120.05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cari Müşteri 04 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 05 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>39591.81</v>
+        <v>121970.98</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -613,16 +613,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>120.05</t>
+          <t>120.06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cari Müşteri 05 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 06 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36591.29</v>
+        <v>112155.14</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -631,16 +631,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>120.06</t>
+          <t>120.07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cari Müşteri 06 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 07 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33646.54</v>
+        <v>102533.78</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -649,16 +649,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>120.07</t>
+          <t>120.08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cari Müşteri 07 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 08 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30760.13</v>
+        <v>93116.55</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -667,16 +667,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>120.08</t>
+          <t>120.09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cari Müşteri 08 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 09 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27934.97</v>
+        <v>83914.33</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -685,16 +685,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>120.09</t>
+          <t>120.10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cari Müşteri 09 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 10 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25174.3</v>
+        <v>74939.53999999999</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -703,16 +703,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>120.10</t>
+          <t>120.11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cari Müşteri 10 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 11 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22481.86</v>
+        <v>66206.49000000001</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -721,16 +721,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>120.11</t>
+          <t>120.12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cari Müşteri 11 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 12 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19861.95</v>
+        <v>57731.89</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>120.12</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cari Müşteri 12 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 13 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17319.57</v>
+        <v>49535.61</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -757,16 +757,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>120.14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cari Müşteri 13 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 14 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14860.68</v>
+        <v>41641.66</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -775,16 +775,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>120.14</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cari Müşteri 14 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 15 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12492.5</v>
+        <v>34079.81</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -793,16 +793,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cari Müşteri 15 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 16 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10223.94</v>
+        <v>26888.19</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -811,16 +811,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>120.17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cari Müşteri 16 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 17 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8066.46</v>
+        <v>20117.71</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -829,16 +829,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>120.17</t>
+          <t>120.18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cari Müşteri 17 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 18 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6035.31</v>
+        <v>13840.7</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -847,16 +847,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>120.18</t>
+          <t>120.19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cari Müşteri 18 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 19 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4152.21</v>
+        <v>8170.33</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -865,16 +865,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>120.19</t>
+          <t>120.20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cari Müşteri 19 - ModaStyle Portföy</t>
+          <t>Cari Müşteri 20 - ModaStyle Portföy</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2451.1</v>
+        <v>3318.18</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -883,16 +883,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>120.20</t>
+          <t>153.01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cari Müşteri 20 - ModaStyle Portföy</t>
+          <t>Ticari Mallar - Ana Kategori A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>995.46</v>
+        <v>3113300.16</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -901,16 +901,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>153.01</t>
+          <t>153.02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ticari Mallar - Ana Kategori A</t>
+          <t>Ticari Mallar - Sezonluk Kategori B</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3113300.16</v>
+        <v>1698163.72</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -919,16 +919,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>153.02</t>
+          <t>153.03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ticari Mallar - Sezonluk Kategori B</t>
+          <t>Ticari Mallar - Tali Ürün Grubu C</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1698163.73</v>
+        <v>849081.87</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>153.03</t>
+          <t>191.01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ticari Mallar - Tali Ürün Grubu C</t>
+          <t>İndirilecek KDV</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>849081.86</v>
+        <v>675840</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -955,16 +955,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>191.01</t>
+          <t>195.01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>İndirilecek KDV</t>
+          <t>İş Avansları &amp; Personel</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>675840</v>
+        <v>450560</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -973,16 +973,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>195.01</t>
+          <t>254.01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>İş Avansları &amp; Personel</t>
+          <t>Taşıtlar ve Dağıtım Araçları</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>450560</v>
+        <v>2112000</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -991,16 +991,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>254.01</t>
+          <t>255.01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Taşıtlar ve Dağıtım Araçları</t>
+          <t>Demirbaşlar ve Bilgi İşlem</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2112000</v>
+        <v>1267200</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1009,16 +1009,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>255.01</t>
+          <t>260.01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Demirbaşlar ve Bilgi İşlem</t>
+          <t>Haklar &amp; Yazılım Lisansları</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1267200</v>
+        <v>844800</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1027,462 +1027,462 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>260.01</t>
+          <t>257.01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Haklar &amp; Yazılım Lisansları</t>
+          <t>Birikmiş Amortismanlar (-)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>844800</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1478400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>257.01</t>
+          <t>300.01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Birikmiş Amortismanlar (-)</t>
+          <t>Banka Kredileri (BCH / Rotatif Ticari)</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1478400</v>
+        <v>2365440</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>300.01</t>
+          <t>300.02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Banka Kredileri (BCH / Rotatif Ticari)</t>
+          <t>Spot &amp; Taksitli Kredi Anapara Taksitleri</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2365440</v>
+        <v>1013760</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>300.02</t>
+          <t>320.01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spot &amp; Taksitli Kredi Anapara Taksitleri</t>
+          <t>Tedarikçi 01 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1013760</v>
+        <v>278650.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>320.01</t>
+          <t>320.02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tedarikçi 01 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 02 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>278650.6</v>
+        <v>256509.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>320.02</t>
+          <t>320.03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tedarikçi 02 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 03 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>256509.89</v>
+        <v>234683.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>320.03</t>
+          <t>320.04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tedarikçi 03 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 04 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>234683.47</v>
+        <v>213190.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>320.04</t>
+          <t>320.05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tedarikçi 04 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 05 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>213190.56</v>
+        <v>192053.27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>320.05</t>
+          <t>320.06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tedarikçi 05 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 06 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>192053.27</v>
+        <v>171297.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>320.06</t>
+          <t>320.07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tedarikçi 06 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 07 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>171297.28</v>
+        <v>150952.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>320.07</t>
+          <t>320.08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tedarikçi 07 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 08 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>150952.91</v>
+        <v>131056.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>320.08</t>
+          <t>320.09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tedarikçi 08 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 09 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>131056.47</v>
+        <v>111652.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>320.09</t>
+          <t>320.10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tedarikçi 09 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 10 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>111652.42</v>
+        <v>92796.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>320.10</t>
+          <t>320.11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tedarikçi 10 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 11 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>92796.58</v>
+        <v>74561.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>320.11</t>
+          <t>320.12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tedarikçi 11 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 12 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>74561.47</v>
+        <v>57045.64</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>320.12</t>
+          <t>320.13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tedarikçi 12 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 13 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>57045.64</v>
+        <v>40392.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>320.13</t>
+          <t>320.14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tedarikçi 13 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 14 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>40392.06</v>
+        <v>24830.56</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>320.14</t>
+          <t>320.15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tedarikçi 14 - ModaStyle Tedarik</t>
+          <t>Tedarikçi 15 - ModaStyle Tedarik</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>24830.56</v>
+        <v>10808.14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>320.15</t>
+          <t>360.01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tedarikçi 15 - ModaStyle Tedarik</t>
+          <t>Ödenecek Vergi ve Fonlar (KDV/Muhtasar)</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>10808.13</v>
+        <v>506880</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>360.01</t>
+          <t>361.01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ödenecek Vergi ve Fonlar (KDV/Muhtasar)</t>
+          <t>Ödenecek Sosyal Güvenlik Kesintileri</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>506880</v>
+        <v>337920</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>361.01</t>
+          <t>400.01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ödenecek Sosyal Güvenlik Kesintileri</t>
+          <t>Banka Kredileri (Uzun Vadeli Yatırım)</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>337920</v>
+        <v>2252800</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>400.01</t>
-        </is>
+      <c r="A55" t="n">
+        <v>500</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Banka Kredileri (Uzun Vadeli Yatırım)</t>
+          <t>Ödenmiş Sermaye</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>2252800</v>
+        <v>1468736.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>500</v>
+        <v>570</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ödenmiş Sermaye</t>
+          <t>Geçmiş Yıllar Kârları</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1468736.88</v>
+        <v>708416.87</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>570</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>600.01</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Geçmiş Yıllar Kârları</t>
+          <t>Yurtiçi Satış Gelirleri</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>708416.88</v>
+        <v>28723200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>600.01</t>
+          <t>611.01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yurtiçi Satış Gelirleri</t>
+          <t>Satış İskontoları (-)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>563200</v>
       </c>
       <c r="D58" t="n">
-        <v>28723200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>611.01</t>
+          <t>621.01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Satış İskontoları (-)</t>
+          <t>Satılan Ticari Mallar Maliyeti (-)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>563200</v>
+        <v>16332800</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>621.01</t>
+          <t>631.01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Satılan Ticari Mallar Maliyeti (-)</t>
+          <t>Pazarlama, Satış ve Dağıtım Giderleri</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>16332800</v>
+        <v>5420800</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1509,16 +1509,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>631.01</t>
+          <t>632.01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pazarlama, Satış ve Dağıtım Giderleri</t>
+          <t>Genel Yönetim Giderleri</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5420800</v>
+        <v>4435200</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1527,16 +1527,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>632.01</t>
+          <t>660.01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Genel Yönetim Giderleri</t>
+          <t>Finansman Giderleri (Ticari Kredi Faizleri)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4435200</v>
+        <v>985600</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1545,36 +1545,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>660.01</t>
+          <t>691.01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Finansman Giderleri (Ticari Kredi Faizleri)</t>
+          <t>Dönem Kârı Vergi ve Yasal Yükümlülükleri</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>985600</v>
+        <v>225280</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>691.01</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Dönem Kârı Vergi ve Yasal Yükümlülükleri</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>225280</v>
-      </c>
-      <c r="D64" t="n">
         <v>0</v>
       </c>
     </row>
